--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -16738,6 +16738,154 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16771,7 +16919,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -16854,7 +17002,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -16864,7 +17012,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1750,9 +1741,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2146,9 +2134,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3282,9 +3267,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3675,9 +3657,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3823,9 +3802,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3971,9 +3947,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4367,9 +4340,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5651,9 +5621,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6044,9 +6011,6 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -6192,9 +6156,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6340,9 +6301,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6736,9 +6694,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7724,9 +7679,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7872,9 +7824,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.0009364932704658844</v>
       </c>
@@ -8020,9 +7969,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8413,9 +8359,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8561,9 +8504,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8709,9 +8649,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9105,9 +9042,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10093,9 +10027,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10241,9 +10172,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10634,9 +10562,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -10782,9 +10707,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10930,9 +10852,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11326,9 +11245,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12462,9 +12378,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12610,9 +12523,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12758,9 +12668,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12906,9 +12813,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -13302,9 +13206,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13698,9 +13599,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -13846,9 +13744,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13994,9 +13889,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14142,9 +14034,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14290,9 +14179,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14438,9 +14324,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14586,9 +14469,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14982,9 +14862,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15378,9 +15255,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15526,9 +15400,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15674,9 +15545,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15822,9 +15690,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15970,9 +15835,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16118,9 +15980,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16266,9 +16125,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16414,9 +16270,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -16808,9 +16661,6 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -12479,12 +12479,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -12523,76 +12523,87 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12619,17 +12630,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -12668,76 +12679,165 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary botulism notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BOTULISM_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12769,12 +12869,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -12808,95 +12908,81 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12923,17 +13009,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -12967,170 +13053,81 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13162,12 +13159,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13201,13 +13198,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13216,7 +13213,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -13241,7 +13238,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -13254,42 +13251,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13321,12 +13318,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13360,29 +13357,29 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Botulisme</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -13407,7 +13404,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -13442,17 +13439,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -13475,7 +13472,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -13488,42 +13485,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13555,12 +13552,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13585,7 +13582,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -13607,68 +13604,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13695,17 +13706,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13730,7 +13741,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -13744,76 +13755,165 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13975,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -14020,7 +14120,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -14135,12 +14235,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -14165,12 +14265,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -14213,42 +14313,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14380,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -14310,12 +14410,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -14358,42 +14458,42 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14425,12 +14525,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -14477,82 +14577,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14579,17 +14665,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -14628,165 +14714,76 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
-        <v>1</v>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14818,12 +14815,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -14872,7 +14869,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -14897,7 +14894,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -14910,42 +14907,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14977,12 +14974,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15023,22 +15020,22 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Botulism</t>
+          <t>Botulisme</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -15063,7 +15060,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -15098,17 +15095,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -15131,7 +15128,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -15144,42 +15141,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15211,12 +15208,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15241,7 +15238,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -15263,68 +15260,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15351,17 +15362,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15386,7 +15397,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -15400,76 +15411,165 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15631,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -15676,7 +15776,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -15821,7 +15921,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -15936,12 +16036,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15966,12 +16066,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -16014,42 +16114,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16081,12 +16181,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16111,12 +16211,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -16159,42 +16259,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16226,12 +16326,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16278,82 +16378,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16380,17 +16466,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16429,165 +16515,76 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16619,118 +16616,511 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>D091</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>肉毒杆菌中毒</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="inlineStr">
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO97" t="inlineStr">
+      <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP97" t="inlineStr">
+      <c r="AP99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR97" t="inlineStr">
+      <c r="AR99" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS97" t="inlineStr"/>
-      <c r="AT97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AV99" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AW99" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="AX99" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="AY99" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="AZ99" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BA99" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BB99" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BC99" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16852,7 +17242,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -16862,7 +17252,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -16882,7 +17272,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -17126,6 +17126,151 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17159,7 +17304,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -17242,7 +17387,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -17252,7 +17397,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -17271,6 +17271,151 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17304,7 +17449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17387,7 +17532,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -17397,7 +17542,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -24914,12 +24914,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -24992,42 +24992,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25059,12 +25059,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -25111,82 +25111,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25199,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -25262,98 +25248,23 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -25447,17 +25358,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -25496,17 +25407,34 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -25514,6 +25442,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -25531,7 +25517,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+          <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -25544,42 +25530,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25606,7 +25592,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -25655,98 +25641,23 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -25840,17 +25751,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -25875,7 +25786,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -25889,76 +25800,165 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25990,12 +25990,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -26020,7 +26020,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -26034,9 +26034,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -26045,77 +26042,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26142,7 +26130,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -26194,98 +26182,18 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -26379,17 +26287,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -26414,7 +26322,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -26428,76 +26336,168 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="R145" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26529,12 +26529,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -26573,9 +26573,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -26584,77 +26581,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26669,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -26733,98 +26721,18 @@
       <c r="P147" t="n">
         <v>0</v>
       </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
-        <v>1</v>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
@@ -26918,17 +26826,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -26953,7 +26861,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -26967,76 +26875,168 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27068,12 +27068,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -27098,7 +27098,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -27112,9 +27112,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -27123,77 +27120,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27208,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -27272,98 +27260,18 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -27457,17 +27365,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -27492,7 +27400,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -27506,76 +27414,168 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27637,7 +27637,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -27796,9 +27796,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -27807,77 +27804,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27904,7 +27892,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -27956,98 +27944,18 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -28141,17 +28049,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -28176,12 +28084,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N155" t="n">
@@ -28190,76 +28098,168 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28291,12 +28291,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -28369,42 +28369,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28436,12 +28436,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -28488,82 +28488,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28590,7 +28576,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -28639,98 +28625,23 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_307_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Botulisme</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -28824,17 +28735,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -28859,7 +28770,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -28873,76 +28784,165 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Botulisme</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_307_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28974,12 +28974,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -29018,9 +29018,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -29029,77 +29026,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29126,7 +29114,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -29178,98 +29166,18 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -29363,17 +29271,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -29398,7 +29306,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -29412,76 +29320,168 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29513,12 +29513,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -29557,9 +29557,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -29568,77 +29565,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29665,7 +29653,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -29717,98 +29705,18 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
@@ -29902,17 +29810,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -29937,7 +29845,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -29951,76 +29859,168 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30052,12 +30052,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -30096,9 +30096,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="P166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30107,77 +30104,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30204,7 +30192,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -30256,98 +30244,18 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_BOTULISM</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>Botulism</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD167" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE167" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF167" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG167" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN167" t="b">
-        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
@@ -30413,6 +30321,243 @@
         </is>
       </c>
       <c r="BC167" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>botulism</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_BOTULISM; SER_SG_HIST_BOTULISM</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -30534,7 +30679,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -30544,7 +30689,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d091/2026-2029.xlsx
+++ b/diseases/d091/2026-2029.xlsx
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1774,17 +1774,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2000,7 +2005,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2008,17 +2013,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2159,7 +2169,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2167,17 +2177,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2393,7 +2408,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2401,17 +2416,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -5548,7 +5568,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5556,17 +5576,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5782,7 +5807,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -5790,17 +5815,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5941,7 +5971,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -5949,17 +5979,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6175,7 +6210,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6183,17 +6218,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9478,7 +9518,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -9486,17 +9526,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -9712,7 +9757,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -9720,17 +9765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -9871,7 +9921,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -9879,17 +9929,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10105,7 +10160,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10113,17 +10168,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -13796,7 +13856,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -13804,17 +13864,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -14030,7 +14095,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -14038,17 +14103,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -14189,7 +14259,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -14197,17 +14267,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -14423,7 +14498,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -14431,17 +14506,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -17575,7 +17655,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -17583,17 +17663,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -17809,7 +17894,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -17817,17 +17902,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -17968,7 +18058,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -17976,17 +18066,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -18202,7 +18297,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -18210,17 +18305,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -21896,7 +21996,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -21904,17 +22004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -22130,7 +22235,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -22138,17 +22243,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -22289,7 +22399,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -22297,17 +22407,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -22523,7 +22638,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -22531,17 +22646,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -25273,7 +25393,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -25281,17 +25401,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS139" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -25507,7 +25632,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
@@ -25515,17 +25640,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS140" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -25666,7 +25796,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -25674,17 +25804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -25900,7 +26035,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -25908,17 +26043,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BOTULISM</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -28650,7 +28790,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -28658,17 +28798,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS158" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -28884,7 +29029,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -28892,17 +29037,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS159" t="inlineStr">
         <is>
           <t>SER_NO_FHI_307_MONTHLY</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
